--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128821168</v>
       </c>
       <c r="B2" t="n">
-        <v>56590</v>
+        <v>56593</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128821158</v>
       </c>
       <c r="B3" t="n">
-        <v>56583</v>
+        <v>56586</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56581</v>
+        <v>56584</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>128821221</v>
       </c>
       <c r="B5" t="n">
-        <v>56604</v>
+        <v>56607</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128821168</v>
       </c>
       <c r="B2" t="n">
-        <v>56593</v>
+        <v>56596</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128821158</v>
       </c>
       <c r="B3" t="n">
-        <v>56586</v>
+        <v>56589</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56584</v>
+        <v>56587</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>128821221</v>
       </c>
       <c r="B5" t="n">
-        <v>56607</v>
+        <v>56610</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128821168</v>
       </c>
       <c r="B2" t="n">
-        <v>56596</v>
+        <v>56598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128821158</v>
       </c>
       <c r="B3" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56587</v>
+        <v>56589</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>128821221</v>
       </c>
       <c r="B5" t="n">
-        <v>56610</v>
+        <v>56612</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>128821168</v>
       </c>
       <c r="B2" t="n">
-        <v>56598</v>
+        <v>56600</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -792,7 +792,7 @@
         <v>128821158</v>
       </c>
       <c r="B3" t="n">
-        <v>56591</v>
+        <v>56593</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56589</v>
+        <v>56591</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1039,7 +1039,7 @@
         <v>128821221</v>
       </c>
       <c r="B5" t="n">
-        <v>56612</v>
+        <v>56614</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56591</v>
+        <v>56689</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56689</v>
+        <v>56715</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56715</v>
+        <v>56717</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56717</v>
+        <v>56725</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56725</v>
+        <v>56726</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -906,7 +906,7 @@
         <v>128821098</v>
       </c>
       <c r="B4" t="n">
-        <v>56726</v>
+        <v>56740</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,37 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>128821168</v>
+        <v>128821098</v>
       </c>
       <c r="B2" t="n">
-        <v>56600</v>
+        <v>56814</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>205992</v>
+        <v>100015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vattenfladdermus</t>
+          <t>Barbastell</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Myotis daubentonii</t>
+          <t>Barbastella barbastellus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Kuhl, 1817)</t>
+          <t>(Schreber, 1774)</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>34</t>
+          <t>2</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -774,7 +774,26 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AT2" t="inlineStr"/>
+      <c r="AS2" t="inlineStr">
+        <is>
+          <t>Johanna Kammonen</t>
+        </is>
+      </c>
+      <c r="AT2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
+      <c r="AU2" t="inlineStr">
+        <is>
+          <t>Espen Jensen</t>
+        </is>
+      </c>
+      <c r="AV2" t="inlineStr">
+        <is>
+          <t>2025</t>
+        </is>
+      </c>
       <c r="AW2" t="inlineStr">
         <is>
           <t>Åsa Duell</t>
@@ -789,37 +808,37 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>128821158</v>
+        <v>128821168</v>
       </c>
       <c r="B3" t="n">
-        <v>56593</v>
+        <v>56823</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>205998</v>
+        <v>205992</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Nordfladdermus</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Eptesicus nilssonii</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>58</t>
+          <t>34</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -903,37 +922,37 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>128821098</v>
+        <v>128821423</v>
       </c>
       <c r="B4" t="n">
-        <v>56746</v>
+        <v>56823</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100015</v>
+        <v>205992</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Barbastell</t>
+          <t>Vattenfladdermus</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Barbastella barbastellus</t>
+          <t>Myotis daubentonii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Schreber, 1774)</t>
+          <t>(Kuhl, 1817)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>44</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -951,14 +970,14 @@
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Södra Viken, Sunne 1, Vrm</t>
+          <t>Södra Viken, Sunne 2, Vrm</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>388727</v>
+        <v>388734</v>
       </c>
       <c r="R4" t="n">
-        <v>6638381</v>
+        <v>6638447</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -1002,26 +1021,7 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AS4" t="inlineStr">
-        <is>
-          <t>Johanna Kammonen</t>
-        </is>
-      </c>
-      <c r="AT4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
-      <c r="AU4" t="inlineStr">
-        <is>
-          <t>Espen Jensen</t>
-        </is>
-      </c>
-      <c r="AV4" t="inlineStr">
-        <is>
-          <t>2025</t>
-        </is>
-      </c>
+      <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
           <t>Åsa Duell</t>
@@ -1036,10 +1036,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>128821221</v>
+        <v>128821158</v>
       </c>
       <c r="B5" t="n">
-        <v>56614</v>
+        <v>56816</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,26 +1047,26 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>206002</v>
+        <v>205998</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunlångöra</t>
+          <t>Nordfladdermus</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Plecotus auritus</t>
+          <t>Eptesicus nilssonii</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>58</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1126,11 +1126,6 @@
           <t>2025-07-25</t>
         </is>
       </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>15 av inspelningarna var sociala läten</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1152,6 +1147,591 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>128821458</v>
+      </c>
+      <c r="B6" t="n">
+        <v>56816</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>205998</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Nordfladdermus</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Eptesicus nilssonii</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(A.Keyserling &amp; Blasius, 1839)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>33</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Södra Viken, Sunne 2, Vrm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>388734</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6638447</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>128821221</v>
+      </c>
+      <c r="B7" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
+      <c r="L7" t="inlineStr"/>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Södra Viken, Sunne 1, Vrm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>388727</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6638381</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>15 av inspelningarna var sociala läten</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>128821409</v>
+      </c>
+      <c r="B8" t="n">
+        <v>56837</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>206002</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Brunlångöra</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Plecotus auritus</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr"/>
+      <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Södra Viken, Sunne 2, Vrm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>388734</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6638447</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-07-23</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>128822560</v>
+      </c>
+      <c r="B9" t="n">
+        <v>58790</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>208245</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Vanlig padda</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Bufo bufo</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Södra viken stugor, Vrm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>388734</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6638415</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-07-25</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF9" t="inlineStr"/>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>128822600</v>
+      </c>
+      <c r="B10" t="n">
+        <v>58817</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>208249</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Vanlig groda</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Rana temporaria</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>ex.</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>i vatten/simmande</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Södra Viken småvatten, Vrm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>388714</v>
+      </c>
+      <c r="R10" t="n">
+        <v>6638429</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2025-08-07</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF10" t="inlineStr"/>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Åsa Duell</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ10"/>
+  <dimension ref="A1:AZ11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1780,6 +1780,126 @@
       <c r="AZ10" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/128822600</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>136251123</v>
+      </c>
+      <c r="B11" t="n">
+        <v>98723</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220007</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Missne</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Calla palustris</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="J11" t="inlineStr"/>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr"/>
+      <c r="N11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Södra Viken, Södra Viken, Vrm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>388732</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6638406</v>
+      </c>
+      <c r="S11" t="n">
+        <v>11</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Värmland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Sunne</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>11:01</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Jens Johansen</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/136251123</t>
         </is>
       </c>
     </row>
@@ -1794,6 +1914,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98723</v>
+        <v>98724</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98724</v>
+        <v>98730</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98730</v>
+        <v>98731</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98731</v>
+        <v>98742</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98742</v>
+        <v>98755</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98755</v>
+        <v>98756</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98756</v>
+        <v>98769</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>

--- a/artfynd/A 47107-2024 artfynd.xlsx
+++ b/artfynd/A 47107-2024 artfynd.xlsx
@@ -1788,7 +1788,7 @@
         <v>136251123</v>
       </c>
       <c r="B11" t="n">
-        <v>98769</v>
+        <v>98770</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
